--- a/artfynd/A 5686-2024 artfynd.xlsx
+++ b/artfynd/A 5686-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120179691</v>
+        <v>120179686</v>
       </c>
       <c r="B2" t="n">
-        <v>97825</v>
+        <v>97882</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223591</v>
+        <v>219797</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716718</v>
+        <v>716701</v>
       </c>
       <c r="R2" t="n">
-        <v>6411439</v>
+        <v>6411473</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120179706</v>
+        <v>120179705</v>
       </c>
       <c r="B3" t="n">
-        <v>97825</v>
+        <v>97892</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,26 +807,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223591</v>
+        <v>219799</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120179698</v>
+        <v>120179704</v>
       </c>
       <c r="B4" t="n">
-        <v>98579</v>
+        <v>97909</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,50 +919,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222322</v>
+        <v>219811</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DC.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716673</v>
+        <v>716658</v>
       </c>
       <c r="R4" t="n">
-        <v>6411433</v>
+        <v>6411468</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1023,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120179694</v>
+        <v>120180519</v>
       </c>
       <c r="B5" t="n">
-        <v>97818</v>
+        <v>57557</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,31 +1026,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223578</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Äkta ängsnycklar</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. incarnata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1068,13 +1063,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716683</v>
+        <v>716904</v>
       </c>
       <c r="R5" t="n">
-        <v>6411429</v>
+        <v>6411391</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,11 +1101,6 @@
           <t>2024-07-03</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rosa blommor.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1119,11 +1109,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Älväxingmyr.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1140,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120179693</v>
+        <v>120179697</v>
       </c>
       <c r="B6" t="n">
-        <v>97944</v>
+        <v>97892</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,43 +1141,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219875</v>
+        <v>219799</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716718</v>
+        <v>716673</v>
       </c>
       <c r="R6" t="n">
-        <v>6411439</v>
+        <v>6411433</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,6 +1203,11 @@
           <t>2024-07-03</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1238,7 +1219,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Fuktskog mot hygge..</t>
+          <t>Älväxingmyr.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1256,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120180519</v>
+        <v>120179691</v>
       </c>
       <c r="B7" t="n">
-        <v>57557</v>
+        <v>97825</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,35 +1249,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103012</v>
+        <v>223591</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1305,13 +1286,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716904</v>
+        <v>716718</v>
       </c>
       <c r="R7" t="n">
-        <v>6411391</v>
+        <v>6411439</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1351,6 +1332,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Fuktskog mot hygge..</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1367,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120179686</v>
+        <v>120180507</v>
       </c>
       <c r="B8" t="n">
-        <v>97882</v>
+        <v>56621</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,21 +1369,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219797</v>
+        <v>100038</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1405,9 +1391,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1416,13 +1402,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716701</v>
+        <v>716583</v>
       </c>
       <c r="R8" t="n">
-        <v>6411473</v>
+        <v>6411509</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1462,11 +1448,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Fuktskog mot hygge..</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1483,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120180507</v>
+        <v>120180508</v>
       </c>
       <c r="B9" t="n">
-        <v>56621</v>
+        <v>57793</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100038</v>
+        <v>102625</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Ficedula albicollis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Temminck, 1795)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1523,7 +1504,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1532,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716583</v>
+        <v>716597</v>
       </c>
       <c r="R9" t="n">
-        <v>6411509</v>
+        <v>6411517</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1594,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120179692</v>
+        <v>120179694</v>
       </c>
       <c r="B10" t="n">
-        <v>97892</v>
+        <v>97818</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,34 +1591,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219799</v>
+        <v>223578</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Äkta ängsnycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716718</v>
+        <v>716683</v>
       </c>
       <c r="R10" t="n">
-        <v>6411439</v>
+        <v>6411429</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1672,6 +1658,11 @@
           <t>2024-07-03</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rosa blommor.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1683,7 +1674,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Fuktskog mot hygge..</t>
+          <t>Älväxingmyr.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1701,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120179705</v>
+        <v>120179693</v>
       </c>
       <c r="B11" t="n">
-        <v>97892</v>
+        <v>97944</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,26 +1708,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219799</v>
+        <v>219875</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1750,13 +1741,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716658</v>
+        <v>716718</v>
       </c>
       <c r="R11" t="n">
-        <v>6411468</v>
+        <v>6411439</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1799,7 +1790,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Älväxingmyr.</t>
+          <t>Fuktskog mot hygge..</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1817,7 +1808,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120179697</v>
+        <v>120179692</v>
       </c>
       <c r="B12" t="n">
         <v>97892</v>
@@ -1857,10 +1848,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716673</v>
+        <v>716718</v>
       </c>
       <c r="R12" t="n">
-        <v>6411433</v>
+        <v>6411439</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,11 +1886,6 @@
           <t>2024-07-03</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1911,7 +1897,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Älväxingmyr.</t>
+          <t>Fuktskog mot hygge..</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1929,10 +1915,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120179704</v>
+        <v>120179706</v>
       </c>
       <c r="B13" t="n">
-        <v>97909</v>
+        <v>97825</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,24 +1931,33 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219811</v>
+        <v>223591</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
@@ -2036,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120180508</v>
+        <v>120179698</v>
       </c>
       <c r="B14" t="n">
-        <v>57793</v>
+        <v>98579</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2048,35 +2043,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102625</v>
+        <v>222322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Halsbandsflugsnappare</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ficedula albicollis</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Temminck, 1795)</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2085,13 +2080,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716597</v>
+        <v>716673</v>
       </c>
       <c r="R14" t="n">
-        <v>6411517</v>
+        <v>6411433</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2131,6 +2126,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Älväxingmyr.</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">

--- a/artfynd/A 5686-2024 artfynd.xlsx
+++ b/artfynd/A 5686-2024 artfynd.xlsx
@@ -1915,10 +1915,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120179706</v>
+        <v>120179698</v>
       </c>
       <c r="B13" t="n">
-        <v>97825</v>
+        <v>98579</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1927,35 +1927,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223591</v>
+        <v>222322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1964,13 +1964,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716658</v>
+        <v>716673</v>
       </c>
       <c r="R13" t="n">
-        <v>6411468</v>
+        <v>6411433</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120179698</v>
+        <v>120179706</v>
       </c>
       <c r="B14" t="n">
-        <v>98579</v>
+        <v>97825</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2043,35 +2043,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222322</v>
+        <v>223591</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2080,13 +2080,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716673</v>
+        <v>716658</v>
       </c>
       <c r="R14" t="n">
-        <v>6411433</v>
+        <v>6411468</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 5686-2024 artfynd.xlsx
+++ b/artfynd/A 5686-2024 artfynd.xlsx
@@ -1915,10 +1915,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120179698</v>
+        <v>120179706</v>
       </c>
       <c r="B13" t="n">
-        <v>98579</v>
+        <v>97825</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1927,35 +1927,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222322</v>
+        <v>223591</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1964,13 +1964,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716673</v>
+        <v>716658</v>
       </c>
       <c r="R13" t="n">
-        <v>6411433</v>
+        <v>6411468</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120179706</v>
+        <v>120179698</v>
       </c>
       <c r="B14" t="n">
-        <v>97825</v>
+        <v>98579</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2043,35 +2043,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>223591</v>
+        <v>222322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2080,13 +2080,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716658</v>
+        <v>716673</v>
       </c>
       <c r="R14" t="n">
-        <v>6411468</v>
+        <v>6411433</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 5686-2024 artfynd.xlsx
+++ b/artfynd/A 5686-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120179686</v>
       </c>
       <c r="B2" t="n">
-        <v>97882</v>
+        <v>97905</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120179705</v>
+        <v>120179698</v>
       </c>
       <c r="B3" t="n">
-        <v>97892</v>
+        <v>98602</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219799</v>
+        <v>222322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -840,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716658</v>
+        <v>716673</v>
       </c>
       <c r="R3" t="n">
-        <v>6411468</v>
+        <v>6411433</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120179704</v>
+        <v>120180519</v>
       </c>
       <c r="B4" t="n">
-        <v>97909</v>
+        <v>57567</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,38 +919,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219811</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716658</v>
+        <v>716904</v>
       </c>
       <c r="R4" t="n">
-        <v>6411468</v>
+        <v>6411391</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,11 +1002,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Älväxingmyr.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1014,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120180519</v>
+        <v>120179700</v>
       </c>
       <c r="B5" t="n">
-        <v>57557</v>
+        <v>104931</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,43 +1034,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>221137</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716904</v>
+        <v>716658</v>
       </c>
       <c r="R5" t="n">
-        <v>6411391</v>
+        <v>6411468</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1109,6 +1104,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Älväxingmyr.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120179697</v>
+        <v>120180507</v>
       </c>
       <c r="B6" t="n">
-        <v>97892</v>
+        <v>56631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,37 +1141,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219799</v>
+        <v>100038</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716673</v>
+        <v>716583</v>
       </c>
       <c r="R6" t="n">
-        <v>6411433</v>
+        <v>6411509</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,11 +1212,6 @@
           <t>2024-07-03</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1216,11 +1220,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Älväxingmyr.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1237,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120179691</v>
+        <v>120179693</v>
       </c>
       <c r="B7" t="n">
-        <v>97825</v>
+        <v>97967</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,26 +1252,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223591</v>
+        <v>219875</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1353,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120180507</v>
+        <v>120180508</v>
       </c>
       <c r="B8" t="n">
-        <v>56621</v>
+        <v>57803</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100038</v>
+        <v>102625</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Ficedula albicollis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Temminck, 1795)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1393,7 +1392,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1402,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716583</v>
+        <v>716597</v>
       </c>
       <c r="R8" t="n">
-        <v>6411509</v>
+        <v>6411517</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1464,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120180508</v>
+        <v>120179704</v>
       </c>
       <c r="B9" t="n">
-        <v>57793</v>
+        <v>97932</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,43 +1479,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102625</v>
+        <v>219811</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Halsbandsflugsnappare</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ficedula albicollis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Temminck, 1795)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716597</v>
+        <v>716658</v>
       </c>
       <c r="R9" t="n">
-        <v>6411517</v>
+        <v>6411468</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1559,6 +1549,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Älväxingmyr.</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1575,10 +1570,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120179694</v>
+        <v>120179691</v>
       </c>
       <c r="B10" t="n">
-        <v>97818</v>
+        <v>97848</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,22 +1586,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223578</v>
+        <v>223591</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Äkta ängsnycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. incarnata</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1620,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716683</v>
+        <v>716718</v>
       </c>
       <c r="R10" t="n">
-        <v>6411429</v>
+        <v>6411439</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,11 +1657,6 @@
           <t>2024-07-03</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rosa blommor.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1674,7 +1668,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Älväxingmyr.</t>
+          <t>Fuktskog mot hygge..</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1692,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120179693</v>
+        <v>120179697</v>
       </c>
       <c r="B11" t="n">
-        <v>97944</v>
+        <v>97915</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,43 +1702,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219875</v>
+        <v>219799</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716718</v>
+        <v>716673</v>
       </c>
       <c r="R11" t="n">
-        <v>6411439</v>
+        <v>6411433</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1779,6 +1764,11 @@
           <t>2024-07-03</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1790,7 +1780,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Fuktskog mot hygge..</t>
+          <t>Älväxingmyr.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1808,10 +1798,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120179692</v>
+        <v>120179694</v>
       </c>
       <c r="B12" t="n">
-        <v>97892</v>
+        <v>97841</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1824,34 +1814,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219799</v>
+        <v>223578</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Äkta ängsnycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716718</v>
+        <v>716683</v>
       </c>
       <c r="R12" t="n">
-        <v>6411439</v>
+        <v>6411429</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1886,6 +1881,11 @@
           <t>2024-07-03</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rosa blommor.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Fuktskog mot hygge..</t>
+          <t>Älväxingmyr.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1915,10 +1915,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120179706</v>
+        <v>120179705</v>
       </c>
       <c r="B13" t="n">
-        <v>97825</v>
+        <v>97915</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1931,26 +1931,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223591</v>
+        <v>219799</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2031,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120179698</v>
+        <v>120179692</v>
       </c>
       <c r="B14" t="n">
-        <v>98579</v>
+        <v>97915</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2043,47 +2043,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222322</v>
+        <v>219799</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>DC.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716673</v>
+        <v>716718</v>
       </c>
       <c r="R14" t="n">
-        <v>6411433</v>
+        <v>6411439</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2120,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Älväxingmyr.</t>
+          <t>Fuktskog mot hygge..</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2147,10 +2138,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120179700</v>
+        <v>120179706</v>
       </c>
       <c r="B15" t="n">
-        <v>104908</v>
+        <v>97848</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2159,28 +2150,37 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221137</v>
+        <v>223591</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>

--- a/artfynd/A 5686-2024 artfynd.xlsx
+++ b/artfynd/A 5686-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120179686</v>
+        <v>120179705</v>
       </c>
       <c r="B2" t="n">
-        <v>97905</v>
+        <v>97915</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219797</v>
+        <v>219799</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716701</v>
+        <v>716658</v>
       </c>
       <c r="R2" t="n">
-        <v>6411473</v>
+        <v>6411468</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Fuktskog mot hygge..</t>
+          <t>Älväxingmyr.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120179698</v>
+        <v>120179691</v>
       </c>
       <c r="B3" t="n">
-        <v>98602</v>
+        <v>97848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,35 +803,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222322</v>
+        <v>223591</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716673</v>
+        <v>716718</v>
       </c>
       <c r="R3" t="n">
-        <v>6411433</v>
+        <v>6411439</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Älväxingmyr.</t>
+          <t>Fuktskog mot hygge..</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120180519</v>
+        <v>120180508</v>
       </c>
       <c r="B4" t="n">
-        <v>57567</v>
+        <v>57803</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>102625</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Ficedula albicollis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Temminck, 1795)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -956,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716904</v>
+        <v>716597</v>
       </c>
       <c r="R4" t="n">
-        <v>6411391</v>
+        <v>6411517</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120179700</v>
+        <v>120179694</v>
       </c>
       <c r="B5" t="n">
-        <v>104931</v>
+        <v>97841</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,41 +1030,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221137</v>
+        <v>223578</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Äkta ängsnycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716658</v>
+        <v>716683</v>
       </c>
       <c r="R5" t="n">
-        <v>6411468</v>
+        <v>6411429</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,6 +1099,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rosa blommor.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120180507</v>
+        <v>120179706</v>
       </c>
       <c r="B6" t="n">
-        <v>56631</v>
+        <v>97848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,31 +1151,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100038</v>
+        <v>223591</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1174,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716583</v>
+        <v>716658</v>
       </c>
       <c r="R6" t="n">
-        <v>6411509</v>
+        <v>6411468</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1220,6 +1230,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Älväxingmyr.</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1236,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120179693</v>
+        <v>120180507</v>
       </c>
       <c r="B7" t="n">
-        <v>97967</v>
+        <v>56631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,31 +1267,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219875</v>
+        <v>100038</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1285,13 +1300,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716718</v>
+        <v>716583</v>
       </c>
       <c r="R7" t="n">
-        <v>6411439</v>
+        <v>6411509</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,11 +1346,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Fuktskog mot hygge..</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1352,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120180508</v>
+        <v>120180519</v>
       </c>
       <c r="B8" t="n">
-        <v>57803</v>
+        <v>57567</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,25 +1374,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102625</v>
+        <v>103012</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Halsbandsflugsnappare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ficedula albicollis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Temminck, 1795)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1392,7 +1402,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1401,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716597</v>
+        <v>716904</v>
       </c>
       <c r="R8" t="n">
-        <v>6411517</v>
+        <v>6411391</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1463,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120179704</v>
+        <v>120179686</v>
       </c>
       <c r="B9" t="n">
-        <v>97932</v>
+        <v>97905</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,37 +1489,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219811</v>
+        <v>219797</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716658</v>
+        <v>716701</v>
       </c>
       <c r="R9" t="n">
-        <v>6411468</v>
+        <v>6411473</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,7 +1571,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Älväxingmyr.</t>
+          <t>Fuktskog mot hygge..</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1570,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120179691</v>
+        <v>120179698</v>
       </c>
       <c r="B10" t="n">
-        <v>97848</v>
+        <v>98602</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1582,35 +1601,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223591</v>
+        <v>222322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1619,10 +1638,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716718</v>
+        <v>716673</v>
       </c>
       <c r="R10" t="n">
-        <v>6411439</v>
+        <v>6411433</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1687,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Fuktskog mot hygge..</t>
+          <t>Älväxingmyr.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1798,10 +1817,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120179694</v>
+        <v>120179692</v>
       </c>
       <c r="B12" t="n">
-        <v>97841</v>
+        <v>97915</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1814,39 +1833,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223578</v>
+        <v>219799</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Äkta ängsnycklar</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. incarnata</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Epipactis palustris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716683</v>
+        <v>716718</v>
       </c>
       <c r="R12" t="n">
-        <v>6411429</v>
+        <v>6411439</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1881,11 +1895,6 @@
           <t>2024-07-03</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rosa blommor.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1897,7 +1906,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Älväxingmyr.</t>
+          <t>Fuktskog mot hygge..</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1915,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120179705</v>
+        <v>120179704</v>
       </c>
       <c r="B13" t="n">
-        <v>97915</v>
+        <v>97932</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1931,33 +1940,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219799</v>
+        <v>219811</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120179692</v>
+        <v>120179700</v>
       </c>
       <c r="B14" t="n">
-        <v>97915</v>
+        <v>104931</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2043,25 +2043,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219799</v>
+        <v>221137</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2071,13 +2071,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716718</v>
+        <v>716658</v>
       </c>
       <c r="R14" t="n">
-        <v>6411439</v>
+        <v>6411468</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Fuktskog mot hygge..</t>
+          <t>Älväxingmyr.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120179706</v>
+        <v>120179693</v>
       </c>
       <c r="B15" t="n">
-        <v>97848</v>
+        <v>97967</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2154,26 +2154,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223591</v>
+        <v>219875</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2187,13 +2187,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716658</v>
+        <v>716718</v>
       </c>
       <c r="R15" t="n">
-        <v>6411468</v>
+        <v>6411439</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Älväxingmyr.</t>
+          <t>Fuktskog mot hygge..</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 5686-2024 artfynd.xlsx
+++ b/artfynd/A 5686-2024 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120179691</v>
+        <v>120180507</v>
       </c>
       <c r="B3" t="n">
-        <v>97848</v>
+        <v>56631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,31 +807,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223591</v>
+        <v>100038</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -840,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716718</v>
+        <v>716583</v>
       </c>
       <c r="R3" t="n">
-        <v>6411439</v>
+        <v>6411509</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,11 +886,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Fuktskog mot hygge..</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -907,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120180508</v>
+        <v>120179686</v>
       </c>
       <c r="B4" t="n">
-        <v>57803</v>
+        <v>97905</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +918,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102625</v>
+        <v>219797</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Halsbandsflugsnappare</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ficedula albicollis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Temminck, 1795)</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -945,9 +940,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -956,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716597</v>
+        <v>716701</v>
       </c>
       <c r="R4" t="n">
-        <v>6411517</v>
+        <v>6411473</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,6 +997,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Fuktskog mot hygge..</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120179694</v>
+        <v>120180508</v>
       </c>
       <c r="B5" t="n">
-        <v>97841</v>
+        <v>57803</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,27 +1034,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223578</v>
+        <v>102625</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Äkta ängsnycklar</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. incarnata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Ficedula albicollis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Temminck, 1795)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1063,13 +1067,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716683</v>
+        <v>716597</v>
       </c>
       <c r="R5" t="n">
-        <v>6411429</v>
+        <v>6411517</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,11 +1105,6 @@
           <t>2024-07-03</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rosa blommor.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1114,11 +1113,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Älväxingmyr.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1135,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120179706</v>
+        <v>120180519</v>
       </c>
       <c r="B6" t="n">
-        <v>97848</v>
+        <v>57567</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,35 +1141,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223591</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1184,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716658</v>
+        <v>716904</v>
       </c>
       <c r="R6" t="n">
-        <v>6411468</v>
+        <v>6411391</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1230,11 +1224,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Älväxingmyr.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1251,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120180507</v>
+        <v>120179700</v>
       </c>
       <c r="B7" t="n">
-        <v>56631</v>
+        <v>104931</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,47 +1252,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100038</v>
+        <v>221137</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716583</v>
+        <v>716658</v>
       </c>
       <c r="R7" t="n">
-        <v>6411509</v>
+        <v>6411468</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1346,6 +1326,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Älväxingmyr.</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1362,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120180519</v>
+        <v>120179691</v>
       </c>
       <c r="B8" t="n">
-        <v>57567</v>
+        <v>97848</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,35 +1359,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103012</v>
+        <v>223591</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1411,13 +1396,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716904</v>
+        <v>716718</v>
       </c>
       <c r="R8" t="n">
-        <v>6411391</v>
+        <v>6411439</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1457,6 +1442,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Fuktskog mot hygge..</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1473,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120179686</v>
+        <v>120179693</v>
       </c>
       <c r="B9" t="n">
-        <v>97905</v>
+        <v>97967</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,26 +1479,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219797</v>
+        <v>219875</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1522,13 +1512,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716701</v>
+        <v>716718</v>
       </c>
       <c r="R9" t="n">
-        <v>6411473</v>
+        <v>6411439</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1589,10 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120179698</v>
+        <v>120179704</v>
       </c>
       <c r="B10" t="n">
-        <v>98602</v>
+        <v>97932</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,50 +1591,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222322</v>
+        <v>219811</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DC.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716673</v>
+        <v>716658</v>
       </c>
       <c r="R10" t="n">
-        <v>6411433</v>
+        <v>6411468</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1817,10 +1798,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120179692</v>
+        <v>120179694</v>
       </c>
       <c r="B12" t="n">
-        <v>97915</v>
+        <v>97841</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,34 +1814,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219799</v>
+        <v>223578</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Äkta ängsnycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716718</v>
+        <v>716683</v>
       </c>
       <c r="R12" t="n">
-        <v>6411439</v>
+        <v>6411429</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,6 +1881,11 @@
           <t>2024-07-03</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rosa blommor.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1906,7 +1897,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Fuktskog mot hygge..</t>
+          <t>Älväxingmyr.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1924,10 +1915,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120179704</v>
+        <v>120179706</v>
       </c>
       <c r="B13" t="n">
-        <v>97932</v>
+        <v>97848</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1940,24 +1931,33 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219811</v>
+        <v>223591</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120179700</v>
+        <v>120179692</v>
       </c>
       <c r="B14" t="n">
-        <v>104931</v>
+        <v>97915</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2043,25 +2043,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221137</v>
+        <v>219799</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2071,13 +2071,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716658</v>
+        <v>716718</v>
       </c>
       <c r="R14" t="n">
-        <v>6411468</v>
+        <v>6411439</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Älväxingmyr.</t>
+          <t>Fuktskog mot hygge..</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120179693</v>
+        <v>120179698</v>
       </c>
       <c r="B15" t="n">
-        <v>97967</v>
+        <v>98602</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2150,35 +2150,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219875</v>
+        <v>222322</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716718</v>
+        <v>716673</v>
       </c>
       <c r="R15" t="n">
-        <v>6411439</v>
+        <v>6411433</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Fuktskog mot hygge..</t>
+          <t>Älväxingmyr.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 5686-2024 artfynd.xlsx
+++ b/artfynd/A 5686-2024 artfynd.xlsx
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120179691</v>
+        <v>120179693</v>
       </c>
       <c r="B8" t="n">
-        <v>97848</v>
+        <v>97967</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,26 +1363,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223591</v>
+        <v>219875</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1463,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120179693</v>
+        <v>120179691</v>
       </c>
       <c r="B9" t="n">
-        <v>97967</v>
+        <v>97848</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,26 +1479,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219875</v>
+        <v>223591</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">

--- a/artfynd/A 5686-2024 artfynd.xlsx
+++ b/artfynd/A 5686-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120179705</v>
+        <v>120179693</v>
       </c>
       <c r="B2" t="n">
-        <v>97915</v>
+        <v>97967</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219799</v>
+        <v>219875</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716658</v>
+        <v>716718</v>
       </c>
       <c r="R2" t="n">
-        <v>6411468</v>
+        <v>6411439</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Älväxingmyr.</t>
+          <t>Fuktskog mot hygge..</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120180507</v>
+        <v>120180508</v>
       </c>
       <c r="B3" t="n">
-        <v>56631</v>
+        <v>57803</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100038</v>
+        <v>102625</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Ficedula albicollis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Temminck, 1795)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716583</v>
+        <v>716597</v>
       </c>
       <c r="R3" t="n">
-        <v>6411509</v>
+        <v>6411517</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120179686</v>
+        <v>120179697</v>
       </c>
       <c r="B4" t="n">
-        <v>97905</v>
+        <v>97915</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,46 +918,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219797</v>
+        <v>219799</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716701</v>
+        <v>716673</v>
       </c>
       <c r="R4" t="n">
-        <v>6411473</v>
+        <v>6411433</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,6 +980,11 @@
           <t>2024-07-03</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1000,7 +996,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Fuktskog mot hygge..</t>
+          <t>Älväxingmyr.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1018,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120180508</v>
+        <v>120179686</v>
       </c>
       <c r="B5" t="n">
-        <v>57803</v>
+        <v>97905</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,21 +1030,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102625</v>
+        <v>219797</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Halsbandsflugsnappare</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ficedula albicollis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Temminck, 1795)</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1056,9 +1052,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1067,13 +1063,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716597</v>
+        <v>716701</v>
       </c>
       <c r="R5" t="n">
-        <v>6411517</v>
+        <v>6411473</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,6 +1109,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Fuktskog mot hygge..</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1129,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120180519</v>
+        <v>120179698</v>
       </c>
       <c r="B6" t="n">
-        <v>57567</v>
+        <v>98602</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,31 +1146,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103012</v>
+        <v>222322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1178,13 +1179,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716904</v>
+        <v>716673</v>
       </c>
       <c r="R6" t="n">
-        <v>6411391</v>
+        <v>6411433</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,6 +1225,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Älväxingmyr.</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1240,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120179700</v>
+        <v>120179694</v>
       </c>
       <c r="B7" t="n">
-        <v>104931</v>
+        <v>97841</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,41 +1258,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221137</v>
+        <v>223578</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Äkta ängsnycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716658</v>
+        <v>716683</v>
       </c>
       <c r="R7" t="n">
-        <v>6411468</v>
+        <v>6411429</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1316,6 +1327,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rosa blommor.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120179693</v>
+        <v>120179691</v>
       </c>
       <c r="B8" t="n">
-        <v>97967</v>
+        <v>97848</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,26 +1379,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219875</v>
+        <v>223591</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1463,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120179691</v>
+        <v>120179705</v>
       </c>
       <c r="B9" t="n">
-        <v>97848</v>
+        <v>97915</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,26 +1495,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223591</v>
+        <v>219799</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1512,13 +1528,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716718</v>
+        <v>716658</v>
       </c>
       <c r="R9" t="n">
-        <v>6411439</v>
+        <v>6411468</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1561,7 +1577,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Fuktskog mot hygge..</t>
+          <t>Älväxingmyr.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1579,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120179704</v>
+        <v>120180507</v>
       </c>
       <c r="B10" t="n">
-        <v>97932</v>
+        <v>56631</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,34 +1611,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219811</v>
+        <v>100038</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716658</v>
+        <v>716583</v>
       </c>
       <c r="R10" t="n">
-        <v>6411468</v>
+        <v>6411509</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1665,11 +1690,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Älväxingmyr.</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1686,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120179697</v>
+        <v>120179704</v>
       </c>
       <c r="B11" t="n">
-        <v>97915</v>
+        <v>97932</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,21 +1722,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219799</v>
+        <v>219811</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1726,13 +1746,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716673</v>
+        <v>716658</v>
       </c>
       <c r="R11" t="n">
-        <v>6411433</v>
+        <v>6411468</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1762,11 +1782,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-03</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,10 +1813,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120179694</v>
+        <v>120179706</v>
       </c>
       <c r="B12" t="n">
-        <v>97841</v>
+        <v>97848</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1814,22 +1829,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223578</v>
+        <v>223591</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Äkta ängsnycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. incarnata</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1843,13 +1862,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716683</v>
+        <v>716658</v>
       </c>
       <c r="R12" t="n">
-        <v>6411429</v>
+        <v>6411468</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1879,11 +1898,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-03</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rosa blommor.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1915,10 +1929,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120179706</v>
+        <v>120179692</v>
       </c>
       <c r="B13" t="n">
-        <v>97848</v>
+        <v>97915</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1931,46 +1945,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223591</v>
+        <v>219799</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716658</v>
+        <v>716718</v>
       </c>
       <c r="R13" t="n">
-        <v>6411468</v>
+        <v>6411439</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2013,7 +2018,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Älväxingmyr.</t>
+          <t>Fuktskog mot hygge..</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2031,10 +2036,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120179692</v>
+        <v>120180519</v>
       </c>
       <c r="B14" t="n">
-        <v>97915</v>
+        <v>57567</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2043,41 +2048,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219799</v>
+        <v>103012</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716718</v>
+        <v>716904</v>
       </c>
       <c r="R14" t="n">
-        <v>6411439</v>
+        <v>6411391</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2117,11 +2131,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Fuktskog mot hygge..</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2138,10 +2147,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120179698</v>
+        <v>120179700</v>
       </c>
       <c r="B15" t="n">
-        <v>98602</v>
+        <v>104931</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2154,46 +2163,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222322</v>
+        <v>221137</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DC.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716673</v>
+        <v>716658</v>
       </c>
       <c r="R15" t="n">
-        <v>6411433</v>
+        <v>6411468</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>

--- a/artfynd/A 5686-2024 artfynd.xlsx
+++ b/artfynd/A 5686-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120179693</v>
+        <v>120179700</v>
       </c>
       <c r="B2" t="n">
-        <v>97967</v>
+        <v>104931</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219875</v>
+        <v>221137</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716718</v>
+        <v>716658</v>
       </c>
       <c r="R2" t="n">
-        <v>6411439</v>
+        <v>6411468</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Fuktskog mot hygge..</t>
+          <t>Älväxingmyr.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -902,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120179697</v>
+        <v>120180507</v>
       </c>
       <c r="B4" t="n">
-        <v>97915</v>
+        <v>56631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,37 +909,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219799</v>
+        <v>100038</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716673</v>
+        <v>716583</v>
       </c>
       <c r="R4" t="n">
-        <v>6411433</v>
+        <v>6411509</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,11 +980,6 @@
           <t>2024-07-03</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -993,11 +988,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Älväxingmyr.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1014,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120179686</v>
+        <v>120179692</v>
       </c>
       <c r="B5" t="n">
-        <v>97905</v>
+        <v>97915</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,46 +1020,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219797</v>
+        <v>219799</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716701</v>
+        <v>716718</v>
       </c>
       <c r="R5" t="n">
-        <v>6411473</v>
+        <v>6411439</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1130,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120179698</v>
+        <v>120179704</v>
       </c>
       <c r="B6" t="n">
-        <v>98602</v>
+        <v>97932</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,50 +1123,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222322</v>
+        <v>219811</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DC.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716673</v>
+        <v>716658</v>
       </c>
       <c r="R6" t="n">
-        <v>6411433</v>
+        <v>6411468</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1246,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120179694</v>
+        <v>120179697</v>
       </c>
       <c r="B7" t="n">
-        <v>97841</v>
+        <v>97915</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,39 +1234,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223578</v>
+        <v>219799</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Äkta ängsnycklar</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. incarnata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Epipactis palustris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716683</v>
+        <v>716673</v>
       </c>
       <c r="R7" t="n">
-        <v>6411429</v>
+        <v>6411433</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,7 +1298,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rosa blommor.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120179691</v>
+        <v>120180519</v>
       </c>
       <c r="B8" t="n">
-        <v>97848</v>
+        <v>57567</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,35 +1342,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223591</v>
+        <v>103012</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1412,13 +1379,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716718</v>
+        <v>716904</v>
       </c>
       <c r="R8" t="n">
-        <v>6411439</v>
+        <v>6411391</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1458,11 +1425,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Fuktskog mot hygge..</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1595,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120180507</v>
+        <v>120179706</v>
       </c>
       <c r="B10" t="n">
-        <v>56631</v>
+        <v>97848</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,31 +1573,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100038</v>
+        <v>223591</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1644,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716583</v>
+        <v>716658</v>
       </c>
       <c r="R10" t="n">
-        <v>6411509</v>
+        <v>6411468</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1690,6 +1652,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Älväxingmyr.</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1706,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120179704</v>
+        <v>120179693</v>
       </c>
       <c r="B11" t="n">
-        <v>97932</v>
+        <v>97967</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,37 +1689,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219811</v>
+        <v>219875</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716658</v>
+        <v>716718</v>
       </c>
       <c r="R11" t="n">
-        <v>6411468</v>
+        <v>6411439</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1795,7 +1771,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Älväxingmyr.</t>
+          <t>Fuktskog mot hygge..</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1813,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120179706</v>
+        <v>120179698</v>
       </c>
       <c r="B12" t="n">
-        <v>97848</v>
+        <v>98602</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,35 +1801,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223591</v>
+        <v>222322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1862,13 +1838,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716658</v>
+        <v>716673</v>
       </c>
       <c r="R12" t="n">
-        <v>6411468</v>
+        <v>6411433</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1929,10 +1905,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120179692</v>
+        <v>120179694</v>
       </c>
       <c r="B13" t="n">
-        <v>97915</v>
+        <v>97841</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,34 +1921,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219799</v>
+        <v>223578</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Äkta ängsnycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716718</v>
+        <v>716683</v>
       </c>
       <c r="R13" t="n">
-        <v>6411439</v>
+        <v>6411429</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,6 +1988,11 @@
           <t>2024-07-03</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rosa blommor.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2018,7 +2004,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Fuktskog mot hygge..</t>
+          <t>Älväxingmyr.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2036,10 +2022,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120180519</v>
+        <v>120179686</v>
       </c>
       <c r="B14" t="n">
-        <v>57567</v>
+        <v>97905</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2048,25 +2034,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103012</v>
+        <v>219797</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2074,9 +2060,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2085,13 +2071,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716904</v>
+        <v>716701</v>
       </c>
       <c r="R14" t="n">
-        <v>6411391</v>
+        <v>6411473</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2131,6 +2117,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Fuktskog mot hygge..</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2147,10 +2138,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120179700</v>
+        <v>120179691</v>
       </c>
       <c r="B15" t="n">
-        <v>104931</v>
+        <v>97848</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2159,41 +2150,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221137</v>
+        <v>223591</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716658</v>
+        <v>716718</v>
       </c>
       <c r="R15" t="n">
-        <v>6411468</v>
+        <v>6411439</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Älväxingmyr.</t>
+          <t>Fuktskog mot hygge..</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 5686-2024 artfynd.xlsx
+++ b/artfynd/A 5686-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120179700</v>
+        <v>120180508</v>
       </c>
       <c r="B2" t="n">
-        <v>104931</v>
+        <v>57803</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221137</v>
+        <v>102625</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Ficedula albicollis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Temminck, 1795)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716658</v>
+        <v>716597</v>
       </c>
       <c r="R2" t="n">
-        <v>6411468</v>
+        <v>6411517</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,11 +770,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Älväxingmyr.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120180508</v>
+        <v>120179706</v>
       </c>
       <c r="B3" t="n">
-        <v>57803</v>
+        <v>97848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,31 +802,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102625</v>
+        <v>223591</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Halsbandsflugsnappare</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ficedula albicollis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Temminck, 1795)</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716597</v>
+        <v>716658</v>
       </c>
       <c r="R3" t="n">
-        <v>6411517</v>
+        <v>6411468</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,6 +881,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Älväxingmyr.</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -893,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120180507</v>
+        <v>120179693</v>
       </c>
       <c r="B4" t="n">
-        <v>56631</v>
+        <v>97967</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,31 +918,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100038</v>
+        <v>219875</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -942,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716583</v>
+        <v>716718</v>
       </c>
       <c r="R4" t="n">
-        <v>6411509</v>
+        <v>6411439</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,6 +997,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Fuktskog mot hygge..</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1004,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120179692</v>
+        <v>120180507</v>
       </c>
       <c r="B5" t="n">
-        <v>97915</v>
+        <v>56631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,37 +1034,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219799</v>
+        <v>100038</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716718</v>
+        <v>716583</v>
       </c>
       <c r="R5" t="n">
-        <v>6411439</v>
+        <v>6411509</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,11 +1113,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Fuktskog mot hygge..</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1111,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120179704</v>
+        <v>120179686</v>
       </c>
       <c r="B6" t="n">
-        <v>97932</v>
+        <v>97905</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,37 +1145,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219811</v>
+        <v>219797</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716658</v>
+        <v>716701</v>
       </c>
       <c r="R6" t="n">
-        <v>6411468</v>
+        <v>6411473</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,7 +1227,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Älväxingmyr.</t>
+          <t>Fuktskog mot hygge..</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1218,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120179697</v>
+        <v>120179704</v>
       </c>
       <c r="B7" t="n">
-        <v>97915</v>
+        <v>97932</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219799</v>
+        <v>219811</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1258,13 +1285,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716673</v>
+        <v>716658</v>
       </c>
       <c r="R7" t="n">
-        <v>6411433</v>
+        <v>6411468</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1294,11 +1321,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120180519</v>
+        <v>120179697</v>
       </c>
       <c r="B8" t="n">
-        <v>57567</v>
+        <v>97915</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,50 +1364,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103012</v>
+        <v>219799</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716904</v>
+        <v>716673</v>
       </c>
       <c r="R8" t="n">
-        <v>6411391</v>
+        <v>6411433</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,6 +1430,11 @@
           <t>2024-07-03</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1425,6 +1443,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Älväxingmyr.</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1441,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120179705</v>
+        <v>120179691</v>
       </c>
       <c r="B9" t="n">
-        <v>97915</v>
+        <v>97848</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,26 +1480,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219799</v>
+        <v>223591</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1490,13 +1513,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716658</v>
+        <v>716718</v>
       </c>
       <c r="R9" t="n">
-        <v>6411468</v>
+        <v>6411439</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1539,7 +1562,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Älväxingmyr.</t>
+          <t>Fuktskog mot hygge..</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1557,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120179706</v>
+        <v>120179705</v>
       </c>
       <c r="B10" t="n">
-        <v>97848</v>
+        <v>97915</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,26 +1596,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223591</v>
+        <v>219799</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1673,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120179693</v>
+        <v>120179694</v>
       </c>
       <c r="B11" t="n">
-        <v>97967</v>
+        <v>97841</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,26 +1712,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219875</v>
+        <v>223578</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Äkta ängsnycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1722,10 +1741,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716718</v>
+        <v>716683</v>
       </c>
       <c r="R11" t="n">
-        <v>6411439</v>
+        <v>6411429</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,6 +1779,11 @@
           <t>2024-07-03</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rosa blommor.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1771,7 +1795,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Fuktskog mot hygge..</t>
+          <t>Älväxingmyr.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1905,10 +1929,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120179694</v>
+        <v>120179700</v>
       </c>
       <c r="B13" t="n">
-        <v>97841</v>
+        <v>104931</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1917,46 +1941,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223578</v>
+        <v>221137</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Äkta ängsnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. incarnata</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716683</v>
+        <v>716658</v>
       </c>
       <c r="R13" t="n">
-        <v>6411429</v>
+        <v>6411468</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1986,11 +2005,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-03</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rosa blommor.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,10 +2036,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120179686</v>
+        <v>120180519</v>
       </c>
       <c r="B14" t="n">
-        <v>97905</v>
+        <v>57567</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2034,25 +2048,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219797</v>
+        <v>103012</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2060,9 +2074,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2071,13 +2085,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716701</v>
+        <v>716904</v>
       </c>
       <c r="R14" t="n">
-        <v>6411473</v>
+        <v>6411391</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2117,11 +2131,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Fuktskog mot hygge..</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2138,10 +2147,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120179691</v>
+        <v>120179692</v>
       </c>
       <c r="B15" t="n">
-        <v>97848</v>
+        <v>97915</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2154,33 +2163,24 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223591</v>
+        <v>219799</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>

--- a/artfynd/A 5686-2024 artfynd.xlsx
+++ b/artfynd/A 5686-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120179706</v>
+        <v>120180507</v>
       </c>
       <c r="B3" t="n">
-        <v>97848</v>
+        <v>56631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,31 +802,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223591</v>
+        <v>100038</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716658</v>
+        <v>716583</v>
       </c>
       <c r="R3" t="n">
-        <v>6411468</v>
+        <v>6411509</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,11 +881,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Älväxingmyr.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -902,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120179693</v>
+        <v>120179691</v>
       </c>
       <c r="B4" t="n">
-        <v>97967</v>
+        <v>97848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,26 +913,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219875</v>
+        <v>223591</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1018,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120180507</v>
+        <v>120179704</v>
       </c>
       <c r="B5" t="n">
-        <v>56631</v>
+        <v>97932</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,43 +1029,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100038</v>
+        <v>219811</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716583</v>
+        <v>716658</v>
       </c>
       <c r="R5" t="n">
-        <v>6411509</v>
+        <v>6411468</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1113,6 +1099,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Älväxingmyr.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1245,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120179704</v>
+        <v>120179705</v>
       </c>
       <c r="B7" t="n">
-        <v>97932</v>
+        <v>97915</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,24 +1252,33 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219811</v>
+        <v>219799</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120179697</v>
+        <v>120179693</v>
       </c>
       <c r="B8" t="n">
-        <v>97915</v>
+        <v>97967</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,34 +1368,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219799</v>
+        <v>219875</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716673</v>
+        <v>716718</v>
       </c>
       <c r="R8" t="n">
-        <v>6411433</v>
+        <v>6411439</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,11 +1439,6 @@
           <t>2024-07-03</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1446,7 +1450,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Älväxingmyr.</t>
+          <t>Fuktskog mot hygge..</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1464,7 +1468,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120179691</v>
+        <v>120179706</v>
       </c>
       <c r="B9" t="n">
         <v>97848</v>
@@ -1499,7 +1503,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1513,13 +1517,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716718</v>
+        <v>716658</v>
       </c>
       <c r="R9" t="n">
-        <v>6411439</v>
+        <v>6411468</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,7 +1566,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Fuktskog mot hygge..</t>
+          <t>Älväxingmyr.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1580,7 +1584,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120179705</v>
+        <v>120179692</v>
       </c>
       <c r="B10" t="n">
         <v>97915</v>
@@ -1613,29 +1617,20 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716658</v>
+        <v>716718</v>
       </c>
       <c r="R10" t="n">
-        <v>6411468</v>
+        <v>6411439</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1678,7 +1673,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Älväxingmyr.</t>
+          <t>Fuktskog mot hygge..</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1696,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120179694</v>
+        <v>120179700</v>
       </c>
       <c r="B11" t="n">
-        <v>97841</v>
+        <v>104931</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,46 +1703,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223578</v>
+        <v>221137</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Äkta ängsnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. incarnata</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716683</v>
+        <v>716658</v>
       </c>
       <c r="R11" t="n">
-        <v>6411429</v>
+        <v>6411468</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1777,11 +1767,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-03</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rosa blommor.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,10 +1798,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120179698</v>
+        <v>120179697</v>
       </c>
       <c r="B12" t="n">
-        <v>98602</v>
+        <v>97915</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,37 +1810,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222322</v>
+        <v>219799</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DC.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
@@ -1898,6 +1874,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120179700</v>
+        <v>120179694</v>
       </c>
       <c r="B13" t="n">
-        <v>104931</v>
+        <v>97841</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1941,41 +1922,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221137</v>
+        <v>223578</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Äkta ängsnycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716658</v>
+        <v>716683</v>
       </c>
       <c r="R13" t="n">
-        <v>6411468</v>
+        <v>6411429</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2005,6 +1991,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rosa blommor.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2147,10 +2138,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120179692</v>
+        <v>120179698</v>
       </c>
       <c r="B15" t="n">
-        <v>97915</v>
+        <v>98602</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2159,38 +2150,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219799</v>
+        <v>222322</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716718</v>
+        <v>716673</v>
       </c>
       <c r="R15" t="n">
-        <v>6411439</v>
+        <v>6411433</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Fuktskog mot hygge..</t>
+          <t>Älväxingmyr.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
